--- a/data(최종).xlsx
+++ b/data(최종).xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/바탕 화면/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4" documentId="8_{409AC372-5076-4FA4-8D9C-FD779969B2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BACCE97D-B10F-4024-B596-8AD3BED98886}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{52C51346-8DFF-4EB0-8A17-5FC0F11C2619}"/>
+    <workbookView minimized="1" xWindow="8805" yWindow="2107" windowWidth="11565" windowHeight="9308" activeTab="1" xr2:uid="{52C51346-8DFF-4EB0-8A17-5FC0F11C2619}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -234,6 +234,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
